--- a/VH_table.xlsx
+++ b/VH_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex\Desktop\kandid\kandid_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41BCDDF-7BD7-4E6E-AAAC-152A6A9B7C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E669DE-FE79-4694-A479-939D023E7481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{50F59FCE-32E6-46E8-8704-794C7F407FCC}"/>
   </bookViews>
@@ -471,16 +471,16 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -492,13 +492,13 @@
         <v>5.5</v>
       </c>
       <c r="D4">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>37</v>
@@ -513,13 +513,13 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>15.6</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>39</v>
@@ -531,16 +531,16 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>10.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="E6">
         <v>17</v>
       </c>
       <c r="F6">
-        <v>20.2</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>42</v>
@@ -552,16 +552,16 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>11.3</v>
+        <v>13.6</v>
       </c>
       <c r="E7">
         <v>19.5</v>
       </c>
       <c r="F7">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>45</v>
